--- a/data/memories/memory_01/locales/es/documents/finance/Budget Q3.xlsx
+++ b/data/memories/memory_01/locales/es/documents/finance/Budget Q3.xlsx
@@ -433,7 +433,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Q3 Budget Report</t>
+          <t>Informe de presupuesto del tercer trimestre</t>
         </is>
       </c>
     </row>
@@ -445,7 +445,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Interno</t>
         </is>
       </c>
     </row>
@@ -469,55 +469,55 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Finance Department</t>
+          <t>Departamento de Finanzas</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Quarterly Financial Overview</t>
+          <t>Resumen financiero trimestral</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>This document contains the revised financial overview for the third quarter. The figures have been reviewed by Finance and compared against the initial budget draft submitted at the beginning of the planning period.</t>
+          <t>Este documento contiene el resumen financiero revisado para el tercer trimestre. Las cifras han sido revisadas por Finanzas y comparadas con el borrador del presupuesto inicial presentado al comienzo del período de planificación.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Allocated Budget</t>
+          <t>Presupuesto asignado</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Spent</t>
+          <t>Gastado</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Remaining</t>
+          <t>Restante</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Estado</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Operaciones</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -537,14 +537,14 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Terminado</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -564,14 +564,14 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Over Budget</t>
+          <t>Por encima del presupuesto</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Recursos humanos</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -591,14 +591,14 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Terminado</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Instalaciones</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -618,14 +618,14 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Review Required</t>
+          <t>Revisión requerida</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Archive Project</t>
+          <t>Proyecto de archivo</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -645,70 +645,70 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Review Required</t>
+          <t>Revisión requerida</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Financial Observations</t>
+          <t>Observaciones financieras</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>The archive project exceeded the original forecast due to additional labour requirements. During the classification process, several groups of historical documents required manual review before being transferred to the digital archive.</t>
+          <t>El proyecto de archivo superó la previsión original debido a necesidades de mano de obra adicionales. Durante el proceso de clasificación, varios grupos de documentos históricos requirieron revisión manual antes de ser transferidos al archivo digital.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Technology expenses increased slightly due to replacement hardware and additional storage requirements associated with document preservation.</t>
+          <t>Los gastos en tecnología aumentaron ligeramente debido al reemplazo de hardware y requisitos de almacenamiento adicionales asociados con la preservación de documentos.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Approval Notes</t>
+          <t>Notas de aprobación</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>• Finance approval completed.</t>
+          <t>• Aprobación financiera completada.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>• Management review pending.</t>
+          <t>• Revisión de la gestión pendiente.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>• Final presentation update required.</t>
+          <t>• Se requiere actualización de la presentación final.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>• Archive costs must be explained in executive summary.</t>
+          <t>• Los costos de archivo deben explicarse en el resumen ejecutivo.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>This document replaces the previous budget draft. Previous versions must remain archived according to document retention policy.</t>
+          <t>Este documento sustituye al anterior proyecto de presupuesto. Las versiones anteriores deben permanecer archivadas según la política de retención de documentos.</t>
         </is>
       </c>
     </row>
